--- a/FSM Demo.xlsx
+++ b/FSM Demo.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ac/Desktop/U3Demo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{696EE140-034A-EE4C-9878-2FC670E73C93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1A3FF4C-26F6-1C42-BB6B-6C0934E4BC25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16100" xr2:uid="{EE97F448-9E24-FC45-A98C-85990EAB9B03}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16100" activeTab="1" xr2:uid="{EE97F448-9E24-FC45-A98C-85990EAB9B03}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -3618,6 +3619,2480 @@
               </a:solidFill>
             </a:rPr>
             <a:t>4</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>241300</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Rectangle 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5CB958E0-3A86-8A26-1641-15F957544A5B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1066800" y="1739900"/>
+          <a:ext cx="18935700" cy="5613400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>241300</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>685800</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="Rectangle 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{52296413-3FD0-4DFB-19A3-615B8F23DB3B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1892300" y="2425700"/>
+          <a:ext cx="17780000" cy="4343400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="92D050"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>520700</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="Rounded Rectangle 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E208449D-84BB-9E07-11E1-E6F581B1E57C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2171700" y="2794000"/>
+          <a:ext cx="1549400" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>Server</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t> Build</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>558800</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="Rounded Rectangle 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A2BF4EA4-0E02-0E47-BBFA-BBCBA52C3F30}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2209800" y="3429000"/>
+          <a:ext cx="1549400" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>Server</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t> Start listen</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>508000</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>406400</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="Rounded Rectangle 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{465F2CD9-9D00-B940-BE48-EA8E07A209E4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2159000" y="4114800"/>
+          <a:ext cx="1549400" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>Server</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t> Start accept</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>101600</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="Rectangle 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9C1B601C-40F7-5DFB-50D7-37D7042C16FC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3873500" y="2590800"/>
+          <a:ext cx="8610600" cy="3632200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>698500</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>203200</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="Rectangle 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{005260D8-6843-4A6F-E5E8-4BAF6C50B446}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4000500" y="2794000"/>
+          <a:ext cx="1155700" cy="330200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent4"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>server</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
+            <a:t> </a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>546100</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="Rectangle 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{494BED56-50E7-AE45-89E9-BF9EB01EFC04}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5334000" y="3276600"/>
+          <a:ext cx="990600" cy="292100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent4"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>thread</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100"/>
+            <a:t>name</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>698500</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="Rectangle 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{34DABE17-2234-F447-A8B4-36721DC7E861}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6477000" y="3289300"/>
+          <a:ext cx="990600" cy="292100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent4"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>thread</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100"/>
+            <a:t>status</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>127000</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="Rectangle 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC75BF8E-900D-9BA6-4D9F-D44A4B4426F9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5080000" y="8178800"/>
+          <a:ext cx="1041400" cy="266700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>TryAccept</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>673100</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>63500</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="Rectangle 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{713BEBB3-FEA9-E943-9502-19B1C7F925B1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6451600" y="3733800"/>
+          <a:ext cx="1041400" cy="266700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>running</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>393700</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="Rounded Rectangle 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32F39874-9F0A-154D-8961-6280AFB311D7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2146300" y="4826000"/>
+          <a:ext cx="1549400" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t>client valid check</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100" baseline="0"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>203200</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>368300</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="Rectangle 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1AE3D44E-9EBB-6E4E-9C9D-831F4162B480}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7632700" y="3302000"/>
+          <a:ext cx="990600" cy="292100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent4"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>socket</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t> name</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>177800</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>393700</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="Rectangle 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9114938E-E5C2-7247-928F-D127A29D1E9A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7607300" y="3733800"/>
+          <a:ext cx="1041400" cy="266700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>server main</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>508000</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>279400</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="Rectangle 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{48136906-F03D-AC45-B1CE-06928853A8C6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8763000" y="3302000"/>
+          <a:ext cx="1422400" cy="368300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent4"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>generate</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t> new socket</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="Rectangle 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{90A8DF5F-D8C4-FF47-9B94-E73F426DCCA9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8788400" y="3746500"/>
+          <a:ext cx="1346200" cy="266700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>true</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>393700</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="Rectangle 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E6975B38-2A4F-8142-AEB7-2BFE1738A847}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17043400" y="2692400"/>
+          <a:ext cx="6464300" cy="3632200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>673100</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="22" name="Rectangle 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0C747222-CBB8-6145-831B-AE1B9F87EE91}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18618200" y="3759200"/>
+          <a:ext cx="1041400" cy="266700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>TryReceive</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>800100</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="23" name="Rectangle 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ACE5CAC0-CD71-F341-A14B-9E9884BAD0C3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19786600" y="3759200"/>
+          <a:ext cx="1041400" cy="266700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>running</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>292100</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>508000</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="25" name="Rectangle 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F791293-85BB-3E49-912D-4701573B7721}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="20929600" y="3771900"/>
+          <a:ext cx="1041400" cy="266700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>client`s</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t> socket</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>685800</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="27" name="Rectangle 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{453605B8-FAD6-1D45-BC50-21E710E19E4B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="22148800" y="3771900"/>
+          <a:ext cx="1041400" cy="266700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>true</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>101600</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>317500</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="28" name="Rectangle 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4BDA74D7-4D5F-944F-ABBF-56C570CFF220}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5054600" y="8661400"/>
+          <a:ext cx="1041400" cy="266700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>Valid</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t> Check</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>416386</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>723899</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="29" name="Can 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{55D3F1A3-B396-6242-3E0A-EB160EBD792E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12798886" y="2667000"/>
+          <a:ext cx="1133013" cy="1524000"/>
+        </a:xfrm>
+        <a:prstGeom prst="can">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="3">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>Queue -</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>Socket</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>tmp sockets</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>57145</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>179799</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>272513</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>170908</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="34" name="Right Arrow 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{60FE74DF-A3B9-CE9E-405B-989316D252A0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="19781327">
+          <a:off x="11614145" y="3430999"/>
+          <a:ext cx="1040868" cy="397509"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent4">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent4"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>711200</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>101600</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="35" name="Rectangle 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0A396C7E-31DE-D046-88CE-181D22477957}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6489700" y="4178300"/>
+          <a:ext cx="1041400" cy="266700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>running</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>520700</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>127000</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="36" name="Rectangle 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A13902B5-2DF9-7B47-A35D-314AD018A3B3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8775700" y="4191000"/>
+          <a:ext cx="1257300" cy="342900"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>false</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>85167</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>140532</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>279386</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>106917</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="37" name="Right Arrow 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{08E375DD-1F6D-5B40-A5F2-8F57403D319B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="9804573">
+          <a:off x="11642167" y="4001332"/>
+          <a:ext cx="1019719" cy="372785"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent4">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent4"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>378286</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>685799</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="38" name="Can 37">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E360C8C0-D66B-FD42-8E2C-EE1976699D35}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12760786" y="4483100"/>
+          <a:ext cx="1133013" cy="1524000"/>
+        </a:xfrm>
+        <a:prstGeom prst="can">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="3">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>Dic -</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t> Cilent id,</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>Socket</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>valid sockets</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>110888</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>111377</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>339649</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>60049</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="39" name="Right Arrow 38">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C1EFAA56-47DD-CF4A-9E58-7304914D5B74}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="979484">
+          <a:off x="11667888" y="4581777"/>
+          <a:ext cx="1054261" cy="355072"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent4">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent4"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>292100</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="40" name="Rectangle 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{572F69E2-BC28-EB4A-9E9E-BF7C3063F9BE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10363200" y="3302000"/>
+          <a:ext cx="1485900" cy="368300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent4"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>generate</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t> new thread</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>711200</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="41" name="Rectangle 40">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7FE32358-9BFC-444E-B33C-AEBDE7461211}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10401300" y="4279900"/>
+          <a:ext cx="1041400" cy="266700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>true</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>711200</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="42" name="Rectangle 41">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F69FA4C4-78E2-9346-A3A7-A0929C112D96}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10401300" y="3835400"/>
+          <a:ext cx="1041400" cy="266700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>false</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>584200</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>355600</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="45" name="Cube 44">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E10554D2-D147-5776-4770-F970E9B31CCF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17094200" y="2819400"/>
+          <a:ext cx="1422400" cy="1879600"/>
+        </a:xfrm>
+        <a:prstGeom prst="cube">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>class clientIns</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>client</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t> id</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t>socket</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t>send thread</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t>receive thread</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t>send queue</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t>receive queue</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>635000</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>406400</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="46" name="Cube 45">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{952B3FFB-C3E3-9E4C-BBA6-1EA8F46FE767}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3111500" y="7581900"/>
+          <a:ext cx="1422400" cy="1447800"/>
+        </a:xfrm>
+        <a:prstGeom prst="cube">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>class threadIns</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>thread</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>name</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>running</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t> time</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>378286</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>685799</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="47" name="Can 46">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BF40F483-C26F-4D45-A22D-B73C5E33E459}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12760786" y="6489700"/>
+          <a:ext cx="1133013" cy="1524000"/>
+        </a:xfrm>
+        <a:prstGeom prst="can">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="3">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>Dic -</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t> thread name-threadins</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>415687</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>317501</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>161650</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="48" name="Right Arrow 47">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE54E7BD-4012-8E4C-B5AA-01D5DA861FFA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6194187" y="8699500"/>
+          <a:ext cx="727314" cy="199750"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent4">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent4"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>406400</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>622300</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="49" name="Rectangle 48">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6FA0529B-5DF3-0D4D-A00A-64CB45CAEB71}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7010400" y="8674100"/>
+          <a:ext cx="1041400" cy="266700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>Recei</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -3930,4 +6405,14 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{908DB012-DA62-5E4A-A642-40209F799D3B}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/FSM Demo.xlsx
+++ b/FSM Demo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ac/Desktop/U3Demo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1A3FF4C-26F6-1C42-BB6B-6C0934E4BC25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6FF2599-9264-9F44-B557-2B84807E9875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16100" activeTab="1" xr2:uid="{EE97F448-9E24-FC45-A98C-85990EAB9B03}"/>
   </bookViews>
@@ -4067,8 +4067,12 @@
         <a:p>
           <a:pPr algn="l"/>
           <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>server</a:t>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100"/>
+            <a:t>System</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100" baseline="0"/>
+            <a:t> client</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
@@ -4222,67 +4226,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>127000</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>50800</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>342900</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="12" name="Rectangle 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC75BF8E-900D-9BA6-4D9F-D44A4B4426F9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5080000" y="8178800"/>
-          <a:ext cx="1041400" cy="266700"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="dk1"/>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="lt1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>TryAccept</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>673100</xdr:colOff>
       <xdr:row>18</xdr:row>
@@ -4665,23 +4608,419 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>200486</xdr:colOff>
+      <xdr:row>50</xdr:row>
       <xdr:rowOff>50800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>393700</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>507999</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="29" name="Can 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{55D3F1A3-B396-6242-3E0A-EB160EBD792E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10931986" y="10210800"/>
+          <a:ext cx="1133013" cy="1524000"/>
+        </a:xfrm>
+        <a:prstGeom prst="can">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="3">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>Queue -</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>Socket</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>tmp client</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>711200</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>101600</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="35" name="Rectangle 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0A396C7E-31DE-D046-88CE-181D22477957}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6489700" y="4178300"/>
+          <a:ext cx="1041400" cy="266700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>running</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>520700</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>127000</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="36" name="Rectangle 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A13902B5-2DF9-7B47-A35D-314AD018A3B3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8775700" y="4191000"/>
+          <a:ext cx="1257300" cy="342900"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>false</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>292100</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="40" name="Rectangle 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{572F69E2-BC28-EB4A-9E9E-BF7C3063F9BE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10363200" y="3302000"/>
+          <a:ext cx="1485900" cy="368300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent4"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>generate</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t> new thread</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>711200</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="41" name="Rectangle 40">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7FE32358-9BFC-444E-B33C-AEBDE7461211}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10401300" y="4279900"/>
+          <a:ext cx="1041400" cy="266700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>true</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>711200</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="42" name="Rectangle 41">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F69FA4C4-78E2-9346-A3A7-A0929C112D96}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10401300" y="3835400"/>
+          <a:ext cx="1041400" cy="266700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>false</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>317500</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>88900</xdr:colOff>
+      <xdr:row>58</xdr:row>
       <xdr:rowOff>25400</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="18" name="Rectangle 17">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E6975B38-2A4F-8142-AEB7-2BFE1738A847}"/>
+        <xdr:cNvPr id="45" name="Cube 44">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E10554D2-D147-5776-4770-F970E9B31CCF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4689,10 +5028,233 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="17043400" y="2692400"/>
-          <a:ext cx="6464300" cy="3632200"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
+          <a:off x="2794000" y="9550400"/>
+          <a:ext cx="1422400" cy="2260600"/>
+        </a:xfrm>
+        <a:prstGeom prst="cube">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>class clientIns</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>function name</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>client</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t> id</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t>socket</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t>send thread</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t>receive thread</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t>send queue</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t>receive queue</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>bool isValid</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>736600</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>508000</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="46" name="Cube 45">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{952B3FFB-C3E3-9E4C-BBA6-1EA8F46FE767}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="736600" y="10350500"/>
+          <a:ext cx="1422400" cy="1447800"/>
+        </a:xfrm>
+        <a:prstGeom prst="cube">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>class threadIns</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>thread</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>name</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>running</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t> time</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="Line Callout 1 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A3861BA-F4BF-46B0-B706-E06B477DEBE6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10287000" y="8966200"/>
+          <a:ext cx="1841500" cy="812800"/>
+        </a:xfrm>
+        <a:prstGeom prst="borderCallout1">
           <a:avLst/>
         </a:prstGeom>
       </xdr:spPr>
@@ -4717,31 +5279,38 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:endParaRPr lang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>457200</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>101600</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>673100</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>165100</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="22" name="Rectangle 21">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0C747222-CBB8-6145-831B-AE1B9F87EE91}"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>5</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t> seconds receive no message, close socket, abort thread</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>390287</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>292101</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>199750</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="44" name="Right Arrow 43">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C0B6CEC0-C200-B444-833A-DC5043EDAB34}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4749,407 +5318,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="18618200" y="3759200"/>
-          <a:ext cx="1041400" cy="266700"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="dk1"/>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="lt1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>TryReceive</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>800100</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>101600</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>165100</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="23" name="Rectangle 22">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ACE5CAC0-CD71-F341-A14B-9E9884BAD0C3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="19786600" y="3759200"/>
-          <a:ext cx="1041400" cy="266700"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="dk1"/>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="lt1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>running</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>292100</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>508000</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>177800</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="25" name="Rectangle 24">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F791293-85BB-3E49-912D-4701573B7721}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="20929600" y="3771900"/>
-          <a:ext cx="1041400" cy="266700"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="dk1"/>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="lt1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>client`s</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0"/>
-            <a:t> socket</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>685800</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>177800</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="27" name="Rectangle 26">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{453605B8-FAD6-1D45-BC50-21E710E19E4B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="22148800" y="3771900"/>
-          <a:ext cx="1041400" cy="266700"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="dk1"/>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="lt1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>true</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>101600</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>127000</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>317500</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>190500</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="28" name="Rectangle 27">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4BDA74D7-4D5F-944F-ABBF-56C570CFF220}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5054600" y="8661400"/>
-          <a:ext cx="1041400" cy="266700"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="dk1"/>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="lt1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>Valid</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0"/>
-            <a:t> Check</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>416386</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>723899</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>127000</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="29" name="Can 28">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{55D3F1A3-B396-6242-3E0A-EB160EBD792E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="12798886" y="2667000"/>
-          <a:ext cx="1133013" cy="1524000"/>
-        </a:xfrm>
-        <a:prstGeom prst="can">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:schemeClr val="accent2"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent2"/>
-        </a:fillRef>
-        <a:effectRef idx="3">
-          <a:schemeClr val="accent2"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>Queue -</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0"/>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>Socket</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>tmp sockets</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1100" baseline="0"/>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>57145</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>179799</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>272513</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>170908</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="34" name="Right Arrow 33">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{60FE74DF-A3B9-CE9E-405B-989316D252A0}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="19781327">
-          <a:off x="11614145" y="3430999"/>
-          <a:ext cx="1040868" cy="397509"/>
+          <a:off x="6168787" y="9347200"/>
+          <a:ext cx="727314" cy="199750"/>
         </a:xfrm>
         <a:prstGeom prst="rightArrow">
           <a:avLst/>
@@ -5184,23 +5354,342 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>136986</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>444499</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="51" name="Can 50">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{55969253-9F0C-EC4A-AC53-2A29FF33A068}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="962486" y="8166100"/>
+          <a:ext cx="1133013" cy="1524000"/>
+        </a:xfrm>
+        <a:prstGeom prst="can">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="3">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>Dic -</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t> System ClientIns</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>101600</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>330200</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="21" name="Straight Arrow Connector 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F35F5833-7B9F-A938-CF6E-1B8C4CB8455A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="1752600" y="10769600"/>
+          <a:ext cx="1054100" cy="88900"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>88900</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>355600</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="52" name="Straight Arrow Connector 51">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B7D0525-5EF7-3747-A110-11934B5C13A7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="1739900" y="10858500"/>
+          <a:ext cx="1092200" cy="63500"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>584200</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>660400</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="53" name="Cube 52">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5522595A-87E5-8548-8512-644A3A53B4F5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4711700" y="9664700"/>
+          <a:ext cx="5029200" cy="2362200"/>
+        </a:xfrm>
+        <a:prstGeom prst="cube">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>class clientIns</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>client</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t> id: 0</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t>socket: new socket</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t>send thread: none</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t>receive thread: keep accept new cilent, put client to Queue-Tmp Client</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t>send queue: none</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t>receive queue: none</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>bool isValid:</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t> true</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>711200</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>101600</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>50</xdr:row>
       <xdr:rowOff>177800</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="35" name="Rectangle 34">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0A396C7E-31DE-D046-88CE-181D22477957}"/>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="Rectangle 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC75BF8E-900D-9BA6-4D9F-D44A4B4426F9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5208,7 +5697,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6489700" y="4178300"/>
+          <a:off x="5791200" y="10337800"/>
           <a:ext cx="1041400" cy="266700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5236,32 +5725,32 @@
           <a:pPr algn="l"/>
           <a:r>
             <a:rPr lang="en-US" sz="1100"/>
-            <a:t>running</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>520700</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>127000</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>127000</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>63500</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="36" name="Rectangle 35">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A13902B5-2DF9-7B47-A35D-314AD018A3B3}"/>
+            <a:t>TryAccept</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>390286</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>88899</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>174350</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="48" name="Right Arrow 47">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE54E7BD-4012-8E4C-B5AA-01D5DA861FFA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5269,69 +5758,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8775700" y="4191000"/>
-          <a:ext cx="1257300" cy="342900"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="dk1"/>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="lt1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>false</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>85167</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>140532</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>279386</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>106917</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="37" name="Right Arrow 36">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{08E375DD-1F6D-5B40-A5F2-8F57403D319B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="9804573">
-          <a:off x="11642167" y="4001332"/>
-          <a:ext cx="1019719" cy="372785"/>
+          <a:off x="9470786" y="10528300"/>
+          <a:ext cx="1349613" cy="212450"/>
         </a:xfrm>
         <a:prstGeom prst="rightArrow">
           <a:avLst/>
@@ -5366,23 +5794,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>378286</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>685799</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="38" name="Can 37">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E360C8C0-D66B-FD42-8E2C-EE1976699D35}"/>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>393700</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>469900</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="54" name="Cube 53">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{04063273-867B-7044-AB69-DEDB125312A4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5390,7 +5818,335 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12760786" y="4483100"/>
+          <a:off x="4521200" y="12242800"/>
+          <a:ext cx="5029200" cy="2362200"/>
+        </a:xfrm>
+        <a:prstGeom prst="cube">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>class clientIns</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>client</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t> id: 0</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t>socket: new socket</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t>send thread: none</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t>receive thread:  every  1 seconfs deque tmp client. check buffer is valid. if true, add it to user client. if false, enque tmp client. if thread time &gt;5, clost socket , abort thread</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t>send queue: none</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t>receive queue: none</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>bool isValid:</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t> true</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>254000</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="28" name="Rectangle 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4BDA74D7-4D5F-944F-ABBF-56C570CFF220}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5816600" y="12928600"/>
+          <a:ext cx="1041400" cy="266700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>Valid</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t> Check</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>800100</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>50800</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="55" name="Cube 54">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{90C65DE8-9BBF-A948-BF07-BC99568D4F63}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12357100" y="9677400"/>
+          <a:ext cx="5029200" cy="2362200"/>
+        </a:xfrm>
+        <a:prstGeom prst="cube">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>class clientIns</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>client</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t> id: new int</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t>socket:  inhert socket</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t>send thread: classic send thread</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t>receive thread: classic recv thread, auto start</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t>send queue: new byte[] 256</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t>receive queue: new byte[] 256</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t>bool isValid: false</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>479886</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>787399</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="56" name="Can 55">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B5BBF59-9C24-5248-AC79-70926043C5F8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1305386" y="12903200"/>
           <a:ext cx="1133013" cy="1524000"/>
         </a:xfrm>
         <a:prstGeom prst="can">
@@ -5425,20 +6181,8 @@
           <a:pPr algn="l"/>
           <a:r>
             <a:rPr lang="en-US" sz="1100" baseline="0"/>
-            <a:t> Cilent id,</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>Socket</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>valid sockets</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t> user ClientIns</a:t>
+          </a:r>
         </a:p>
         <a:p>
           <a:pPr algn="l"/>
@@ -5450,32 +6194,32 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>110888</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>111377</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>339649</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>60049</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="39" name="Right Arrow 38">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C1EFAA56-47DD-CF4A-9E58-7304914D5B74}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="979484">
-          <a:off x="11667888" y="4581777"/>
-          <a:ext cx="1054261" cy="355072"/>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>720486</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>419099</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>199750</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="58" name="Right Arrow 57">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B31A1A79-634E-424A-A516-CA876C89C764}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="9376514">
+          <a:off x="9800986" y="11976100"/>
+          <a:ext cx="1349613" cy="212450"/>
         </a:xfrm>
         <a:prstGeom prst="rightArrow">
           <a:avLst/>
@@ -5510,502 +6254,32 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>457200</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>50800</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>292100</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="40" name="Rectangle 39">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{572F69E2-BC28-EB4A-9E9E-BF7C3063F9BE}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10363200" y="3302000"/>
-          <a:ext cx="1485900" cy="368300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent4"/>
-        </a:lnRef>
-        <a:fillRef idx="2">
-          <a:schemeClr val="accent4"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent4"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>generate</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0"/>
-            <a:t> new thread</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>495300</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>187087</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>114301</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>711200</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="41" name="Rectangle 40">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7FE32358-9BFC-444E-B33C-AEBDE7461211}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10401300" y="4279900"/>
-          <a:ext cx="1041400" cy="266700"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="dk1"/>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="lt1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>true</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>495300</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>177800</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>711200</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="42" name="Rectangle 41">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F69FA4C4-78E2-9346-A3A7-A0929C112D96}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10401300" y="3835400"/>
-          <a:ext cx="1041400" cy="266700"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="dk1"/>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="lt1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>false</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>584200</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>177800</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>355600</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="45" name="Cube 44">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E10554D2-D147-5776-4770-F970E9B31CCF}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="17094200" y="2819400"/>
-          <a:ext cx="1422400" cy="1879600"/>
-        </a:xfrm>
-        <a:prstGeom prst="cube">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent2">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent2"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent2"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>class clientIns</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="en-US" sz="1100"/>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>client</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0"/>
-            <a:t> id</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0"/>
-            <a:t>socket</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0"/>
-            <a:t>send thread</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0"/>
-            <a:t>receive thread</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0"/>
-            <a:t>send queue</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0"/>
-            <a:t>receive queue</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>635000</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>63500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>406400</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>88900</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="46" name="Cube 45">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{952B3FFB-C3E3-9E4C-BBA6-1EA8F46FE767}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3111500" y="7581900"/>
-          <a:ext cx="1422400" cy="1447800"/>
-        </a:xfrm>
-        <a:prstGeom prst="cube">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent2">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent2"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent2"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>class threadIns</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="en-US" sz="1100"/>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>thread</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>name</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>running</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0"/>
-            <a:t> time</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>378286</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>190500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>685799</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>88900</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="47" name="Can 46">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BF40F483-C26F-4D45-A22D-B73C5E33E459}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="12760786" y="6489700"/>
-          <a:ext cx="1133013" cy="1524000"/>
-        </a:xfrm>
-        <a:prstGeom prst="can">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:schemeClr val="accent2"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent2"/>
-        </a:fillRef>
-        <a:effectRef idx="3">
-          <a:schemeClr val="accent2"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>Dic -</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0"/>
-            <a:t> thread name-threadins</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1100"/>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>415687</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>165100</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>317501</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>161650</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="48" name="Right Arrow 47">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE54E7BD-4012-8E4C-B5AA-01D5DA861FFA}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6194187" y="8699500"/>
-          <a:ext cx="727314" cy="199750"/>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>123551</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="59" name="Right Arrow 58">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B5A40798-7A03-9A45-8D71-9E94E0094202}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="10363479">
+          <a:off x="2663587" y="13119101"/>
+          <a:ext cx="1349613" cy="212450"/>
         </a:xfrm>
         <a:prstGeom prst="rightArrow">
           <a:avLst/>
@@ -6040,23 +6314,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>406400</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>139700</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>622300</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>762000</xdr:colOff>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="49" name="Rectangle 48">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6FA0529B-5DF3-0D4D-A00A-64CB45CAEB71}"/>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="60" name="Rectangle 59">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{094602DF-717F-1C40-AFB9-D3C919C99CBC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6064,36 +6338,45 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7010400" y="8674100"/>
-          <a:ext cx="1041400" cy="266700"/>
+          <a:off x="4064000" y="4470400"/>
+          <a:ext cx="1384300" cy="330200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
       </xdr:spPr>
       <xdr:style>
-        <a:lnRef idx="2">
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent4"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
           <a:schemeClr val="dk1"/>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="lt1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>Recei</a:t>
-          </a:r>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100"/>
+            <a:t>Comminication</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100" baseline="0"/>
+            <a:t> client</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
+            <a:t> </a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
